--- a/assets/downloads/grille-audit-easy-checks.xlsx
+++ b/assets/downloads/grille-audit-easy-checks.xlsx
@@ -702,7 +702,7 @@
     <row r="1" ht="38" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>IGPDE - Formation 102638 - Grille d'audit 13 points de contrôle rapides du W3C</t>
+          <t>IGPDE - Formation 102846 - Grille d'audit 13 points de contrôle rapides du W3C</t>
         </is>
       </c>
     </row>

--- a/assets/downloads/grille-audit-easy-checks.xlsx
+++ b/assets/downloads/grille-audit-easy-checks.xlsx
@@ -7516,7 +7516,7 @@
       </c>
       <c r="D6" s="11" t="inlineStr">
         <is>
-          <t>53-55</t>
+          <t>84-86</t>
         </is>
       </c>
       <c r="E6" s="12" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>56</t>
+          <t>87</t>
         </is>
       </c>
       <c r="E7" s="12" t="inlineStr">
@@ -7612,7 +7612,7 @@
       </c>
       <c r="D8" s="11" t="inlineStr">
         <is>
-          <t>57-58</t>
+          <t>88-89</t>
         </is>
       </c>
       <c r="E8" s="12" t="inlineStr">
@@ -7660,7 +7660,7 @@
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>59-60</t>
+          <t>90-91</t>
         </is>
       </c>
       <c r="E9" s="12" t="inlineStr">
@@ -7708,7 +7708,7 @@
       </c>
       <c r="D10" s="11" t="inlineStr">
         <is>
-          <t>61</t>
+          <t>92</t>
         </is>
       </c>
       <c r="E10" s="12" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>62-65</t>
+          <t>93-96</t>
         </is>
       </c>
       <c r="E11" s="12" t="inlineStr">
@@ -7804,7 +7804,7 @@
       </c>
       <c r="D12" s="11" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>97</t>
         </is>
       </c>
       <c r="E12" s="12" t="inlineStr">
@@ -7852,7 +7852,7 @@
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>67</t>
+          <t>98</t>
         </is>
       </c>
       <c r="E13" s="12" t="inlineStr">
@@ -7900,7 +7900,7 @@
       </c>
       <c r="D14" s="11" t="inlineStr">
         <is>
-          <t>68-69</t>
+          <t>99-100</t>
         </is>
       </c>
       <c r="E14" s="12" t="inlineStr">
@@ -7948,7 +7948,7 @@
       </c>
       <c r="D15" s="11" t="inlineStr">
         <is>
-          <t>70</t>
+          <t>101</t>
         </is>
       </c>
       <c r="E15" s="12" t="inlineStr">
@@ -7996,7 +7996,7 @@
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>71</t>
+          <t>102</t>
         </is>
       </c>
       <c r="E16" s="12" t="inlineStr">
@@ -8044,7 +8044,7 @@
       </c>
       <c r="D17" s="11" t="inlineStr">
         <is>
-          <t>72-74</t>
+          <t>105-107</t>
         </is>
       </c>
       <c r="E17" s="12" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="D18" s="11" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>108</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">

--- a/assets/downloads/grille-audit-easy-checks.xlsx
+++ b/assets/downloads/grille-audit-easy-checks.xlsx
@@ -691,7 +691,7 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>Titre de page</t>
+          <t>Vérifier le titre de la page</t>
         </is>
       </c>
       <c r="C12" s="7" t="inlineStr">
@@ -728,7 +728,7 @@
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
-          <t>Guide du RGAA</t>
+          <t>Structurer la page avec des titres</t>
         </is>
       </c>
       <c r="D13" s="7" t="inlineStr">
@@ -755,12 +755,12 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>Contraste des couleurs</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>Charte de publication</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
       <c r="D14" s="7" t="inlineStr">
@@ -851,12 +851,12 @@
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>Langue de la page</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
-          <t>Atelier international</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
       <c r="D17" s="7" t="inlineStr">
@@ -1148,7 +1148,7 @@
       </c>
       <c r="B30" s="7" t="inlineStr">
         <is>
-          <t>Guide du RGAA</t>
+          <t>Structurer la page avec des titres</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
@@ -1170,7 +1170,7 @@
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>Charte de publication</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>Atelier international</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="C6" s="8" t="inlineStr">
         <is>
-          <t>Titre de page</t>
+          <t>Vérifier le titre de la page</t>
         </is>
       </c>
       <c r="D6" s="7">
@@ -2520,7 +2520,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>Guide du RGAA</t>
+          <t>Structurer la page avec des titres</t>
         </is>
       </c>
       <c r="C7" s="8" t="inlineStr">
@@ -2549,12 +2549,12 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Charte de publication</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
       <c r="C8" s="8" t="inlineStr">
         <is>
-          <t>Contraste des couleurs</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
       <c r="D8" s="7">
@@ -2636,12 +2636,12 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>Atelier international</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>Langue de la page</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
       <c r="D11" s="7">
@@ -2846,12 +2846,12 @@
   </mergeCells>
   <hyperlinks>
     <hyperlink ref="C5" location="'#01 - Images'!A1" display="Texte alternatif des images"/>
-    <hyperlink ref="C6" location="'#02 - Titre de page'!A1" display="Titre de page"/>
+    <hyperlink ref="C6" location="'#02 - Titre de page'!A1" display="Vérifier le titre de la page"/>
     <hyperlink ref="C7" location="'#03 - Titres'!A1" display="Titres et hiérarchie"/>
-    <hyperlink ref="C8" location="'#04 - Contrastes'!A1" display="Contraste des couleurs"/>
+    <hyperlink ref="C8" location="'#04 - Contrastes'!A1" display="Vérifier le contraste des couleurs"/>
     <hyperlink ref="C9" location="'#05 - Évitement'!A1" display="Lien d'évitement"/>
     <hyperlink ref="C10" location="'#06 - Clavier'!A1" display="Focus et navigation clavier"/>
-    <hyperlink ref="C11" location="'#07 - Langue'!A1" display="Langue de la page"/>
+    <hyperlink ref="C11" location="'#07 - Langue'!A1" display="Déclarer les langues utilisées dans la page"/>
     <hyperlink ref="C12" location="'#08 - Zoom 200 %'!A1" display="Zoom à 200 %"/>
     <hyperlink ref="C13" location="'#09 - Sous-titres'!A1" display="Sous-titres vidéo"/>
     <hyperlink ref="C14" location="'#10 - Transcription'!A1" display="Transcriptions audio et vidéo"/>
@@ -3076,7 +3076,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Titre de page</t>
+          <t>Vérifier le titre de la page</t>
         </is>
       </c>
     </row>
@@ -3112,7 +3112,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>Le titre identifie-t-il clairement la page, la requête et, le cas échéant, la pagination ?</t>
+          <t>Le titre permet-il d'identifier immédiatement la page et son état, avec l'information spécifique en premier ?</t>
         </is>
       </c>
     </row>
@@ -3148,7 +3148,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Lire le titre dans l'onglet du navigateur et dans le code source.</t>
+          <t>Lire le titre dans l'onglet du navigateur. Pour afficher sa valeur complète, utiliser le bookmarklet « 02 Titre de page ». En alternative, afficher le code source, rechercher &lt;title&gt; et lire son contenu.</t>
         </is>
       </c>
     </row>
@@ -3160,7 +3160,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Titre présent et pertinent. Information propre à la page placée avant le nom du site. Titre distinct d'une page à l'autre.</t>
+          <t>Titre présent, pertinent et distinct. La requête et la pagination utiles sont indiquées. L'information propre à la page apparaît avant le nom du site.</t>
         </is>
       </c>
     </row>
@@ -3268,7 +3268,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Guide du RGAA</t>
+          <t>Structurer la page avec des titres</t>
         </is>
       </c>
     </row>
@@ -3328,7 +3328,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Comparer le plan visuel et le plan obtenu avec HeadingsMap ou « Check headings ».</t>
+          <t>Comparer le plan visuel avec les titres identifiés par HeadingsMap, le bookmarklet « 9.1 - Lister les titres » ou WAVE.</t>
         </is>
       </c>
     </row>
@@ -3436,7 +3436,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Contraste des couleurs</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
     </row>
@@ -3448,7 +3448,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Charte de publication</t>
+          <t>Vérifier le contraste des couleurs</t>
         </is>
       </c>
     </row>
@@ -3500,7 +3500,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="55" customHeight="1">
+    <row r="8" ht="78" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Comment tester</t>
@@ -3508,7 +3508,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Mesurer les couleurs avec CCA, WebAIM Contrast Checker ou la pipette des outils de développement.</t>
+          <t>Repérer les contrastes à vérifier avec WCAG Contrast Checker pour Firefox ou WCAG Color contrast checker pour Chrome. Mesurer les couples de couleurs avec Colour Contrast Analyser (CCA) de Vispero ou Tanaguru Contrast-Finder. Attention : les extensions automatiques peuvent produire des faux positifs ; confirmer chaque résultat à partir des couleurs calculées, de la taille du texte et du rôle de l'élément.</t>
         </is>
       </c>
     </row>
@@ -3976,7 +3976,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Langue de la page</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
     </row>
@@ -3988,7 +3988,7 @@
       </c>
       <c r="B3" s="8" t="inlineStr">
         <is>
-          <t>Atelier international</t>
+          <t>Déclarer les langues utilisées dans la page</t>
         </is>
       </c>
     </row>
@@ -4048,7 +4048,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Inspecter l'attribut lang de la page et des passages rédigés dans une autre langue.</t>
+          <t>Afficher les attributs lang et dir avec le bookmarklet « 08 Langue et direction ». En complément, ouvrir le validateur HTML du W3C depuis Web Developer (Outils &gt; Valider le HTML), puis utiliser Tanaguru. Vérifier manuellement que chaque code de langue correspond au contenu.</t>
         </is>
       </c>
     </row>
@@ -4192,7 +4192,7 @@
       </c>
       <c r="B5" s="7" t="inlineStr">
         <is>
-          <t>À 200 % et dans une fenêtre étroite, les contenus restent-ils lisibles et utilisables sans perte d'information ?</t>
+          <t>À 200 %, dans une fenêtre étroite et avec un espacement du texte renforcé, les contenus restent-ils lisibles et utilisables sans perte d'information ?</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="B6" s="7" t="inlineStr">
         <is>
-          <t>1.4.4 - Redimensionnement du texte ; 1.4.10 - Redistribution</t>
+          <t>1.4.4 - Redimensionnement du texte ; 1.4.10 - Redistribution ; 1.4.12 - Espacement du texte</t>
         </is>
       </c>
     </row>
@@ -4216,7 +4216,7 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>10.4, 10.11</t>
+          <t>10.4, 10.11, 10.12</t>
         </is>
       </c>
     </row>
@@ -4228,7 +4228,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Zoomer à 200 %, puis tester séparément une zone d'affichage de 320 CSS px et parcourir tout le contenu.</t>
+          <t>Zoomer à 200 %, puis tester séparément une zone d'affichage de 320 CSS px. Activer ensuite le bookmarklet « 10.12 Espacement » et parcourir tout le contenu.</t>
         </is>
       </c>
     </row>
@@ -4240,7 +4240,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>Aucun texte coupé ou superposé. Contenus et commandes utilisables. Pas de défilement dans deux directions pour lire le contenu courant.</t>
+          <t>Aucun texte coupé ou superposé. Contenus et commandes utilisables. Pas de défilement dans deux directions pour lire le contenu courant. Aucun contenu perdu après modification de l'espacement du texte.</t>
         </is>
       </c>
     </row>

--- a/assets/downloads/grille-audit-easy-checks.xlsx
+++ b/assets/downloads/grille-audit-easy-checks.xlsx
@@ -2124,7 +2124,7 @@
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>Cliquer sur chaque libellé, vérifier le nom accessible et contrôler les légendes des groupes.</t>
+          <t>Repérer les champs et leurs étiquettes avec le bookmarklet « 11.1 Formulaires », Tanaguru ou WAVE. Cliquer sur chaque libellé, vérifier le nom accessible et contrôler les légendes des groupes.</t>
         </is>
       </c>
     </row>
